--- a/fixtures/acceptance/T02_same_cell_conflict_temp/Control.xlsx
+++ b/fixtures/acceptance/T02_same_cell_conflict_temp/Control.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chun\Python\Prophet Table Integration\fixtures\acceptance\T02_same_cell_conflict_temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E47640E-1E6D-4AFF-A9FE-EACEDE521965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5DB30B-FC13-46BB-A0D1-DC2584F1B2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>key</t>
   </si>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>new_column_name</t>
-  </si>
-  <si>
-    <t>C:\Chun\Python\Prophet Table Integration\fixtures\acceptance\T02_same_cell_conflict_temp</t>
   </si>
   <si>
     <t>generate_changelog</t>
@@ -455,16 +452,13 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
